--- a/roles-matrix.xlsx
+++ b/roles-matrix.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,11 +45,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -107,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,7 +110,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -127,22 +122,21 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -510,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -577,43 +571,28 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="7" t="n"/>
-    </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Merged School Portal — Roles Matrix v1 (analysis draft)</t>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Merged School Portal — Roles Matrix v2 (incorporates Alongside review, Jess Bell)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Generated from</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>roles-matrix.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Review by Alongside + TimelyCare experts for accuracy before build</t>
         </is>
       </c>
     </row>
@@ -638,53 +617,53 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Capability</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>District Administrator</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>District Staff</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>School Administrator</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Clinical Staff + NEW</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>School Staff</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Notes / origin</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>User &amp; school management — TimelyCare</t>
         </is>
@@ -701,27 +680,27 @@
           <t>Manage district users</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -743,27 +722,27 @@
           <t>Manage school users (per school)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -785,27 +764,27 @@
           <t>Create / manage schools in district</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -827,27 +806,27 @@
           <t>Allocate invites/visits to schools</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -859,7 +838,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Visits &amp; care — TimelyCare (PHI gated)</t>
         </is>
@@ -876,27 +855,27 @@
           <t>View visit data (aggregate, no PHI)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -918,27 +897,27 @@
           <t>View visit schedule (per student, PHI)</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -960,27 +939,27 @@
           <t>View visit history (student detail, PHI)</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1002,27 +981,27 @@
           <t>View student clinical records</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1044,27 +1023,27 @@
           <t>View / edit insurance status</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1086,27 +1065,27 @@
           <t>Visit facilitation (start/end session)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1128,27 +1107,27 @@
           <t>Invite distribution (refer a student)</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -1170,27 +1149,27 @@
           <t>Invite management (view status)</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1202,7 +1181,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Students &amp; alerts — Alongside</t>
         </is>
@@ -1219,27 +1198,27 @@
           <t>View student roster</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -1261,27 +1240,27 @@
           <t>Download SY roster (CSV)</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1303,27 +1282,27 @@
           <t>View dashboard</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1345,27 +1324,27 @@
           <t>Receive Chat summary alerts</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -1387,27 +1366,27 @@
           <t>Receive Crisis email / SMS alerts</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -1429,27 +1408,27 @@
           <t>Receive Standard message alerts</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -1471,34 +1450,34 @@
           <t>Receive Anonymous message alerts</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>"Tip line" routing.</t>
+          <t>"Tip line" routing. Defaults to School Admin; Clinical Staff configurable. (Jess B., Alongside)</t>
         </is>
       </c>
     </row>
@@ -1513,27 +1492,27 @@
           <t>View screener results (per student)</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1555,39 +1534,39 @@
           <t>Assign skills to students</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Teachers may assign if school enables.</t>
+          <t>Default for classroom teachers — Assign Skills was built for them. (Jess B., Alongside)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Library, reports &amp; insights</t>
         </is>
@@ -1604,27 +1583,27 @@
           <t>View Library (skills, screeners, resources)</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1646,27 +1625,27 @@
           <t>View Reports (download insights)</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1678,7 +1657,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>System</t>
         </is>
@@ -1695,27 +1674,27 @@
           <t>Student Demo (preview mode)</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1737,27 +1716,27 @@
           <t>Self-Care mode (own private space)</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1779,27 +1758,27 @@
           <t>Settings (own profile)</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1832,46 +1811,46 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>District Admin</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>District Staff</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>School Admin</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Clinical Staff</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>School Staff</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>What it gates</t>
         </is>
@@ -1883,29 +1862,29 @@
           <t>PHI Access (default)</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>configurable</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>configurable</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>configurable</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -1917,37 +1896,37 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Org Contact (default)</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>Org Admin (default)</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>ON</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Roster download, escalation routing target. Alongside-native.</t>
+          <t>Roster download, escalation routing target. Called "Org Admin" in Alongside Retool. District Staff configurable — some districts list extra staff here. (Jess B., Alongside)</t>
         </is>
       </c>
     </row>
@@ -1957,34 +1936,34 @@
           <t>Alert subscriptions (default set)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Crisis (E+SMS)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Configurable</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Crisis (E+SMS)</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>All 5</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>Crisis (E+SMS)</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Chat summary, Crisis Email, Crisis SMS, Standard, Anonymous. Per-user override.</t>
+          <t>Chat summary, Crisis Email, Crisis SMS, Standard, Anonymous. Per-user override. District Staff configurable — many districts add student-services / mental-health teams. (Jess B., Alongside)</t>
         </is>
       </c>
     </row>
@@ -1994,34 +1973,34 @@
           <t>Job title (metadata only)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>free text</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>free text</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Principal / Asst Principal / Admin</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Counselor / Social Worker / Psychologist / LCSW / LMFT</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Counselor / LPC / Social Worker / Psychologist / LCSW / LMFT</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Teacher / Coach / Para / Other</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Display only. Used for routing rules and UI labels — does not grant permission.</t>
+          <t>Display only. Used for routing rules and UI labels — does not grant permission. (LPC per Alongside — TX differentiates it from counselor.)</t>
         </is>
       </c>
     </row>

--- a/roles-matrix.xlsx
+++ b/roles-matrix.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>roles-matrix.html</t>
+          <t>roles-matrix.html (retired — this xlsx is the source of truth)</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>View Reports (download insights)</t>
+          <t>View Reports (dashboards &amp; exports)</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -1657,51 +1657,51 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Library, reports &amp; insights</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>View Insights (Alongside AI summary)</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Mirrors Alongside Dashboard — all staff, data filtered by scope. School-scoped AI summary of student conversation themes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>System</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Student Demo (preview mode)</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Sandboxed; no data writes.</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Self-Care mode (own private space)</t>
+          <t>Student Demo (preview mode)</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Universal. Not visible to district.</t>
+          <t>Sandboxed; no data writes.</t>
         </is>
       </c>
     </row>
@@ -1755,35 +1755,77 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
+          <t>Self-Care mode (own private space)</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Universal. Not visible to district.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
           <t>Settings (own profile)</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>All users.</t>
         </is>
@@ -1792,7 +1834,7 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
